--- a/Fee Schedule Automation Tracker.xlsx
+++ b/Fee Schedule Automation Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petauri-my.sharepoint.com/personal/wonmin_song_petauri_com/Documents/Desktop/Fee-Schedule-Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{D9BA4A1E-E287-2A46-A929-6B1241EC5EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A36E2A6F-F728-4AC4-B2DE-435AC7C46D96}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{D9BA4A1E-E287-2A46-A929-6B1241EC5EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A55ECFA-8EB2-486A-B411-41DFEB81824F}"/>
   <bookViews>
-    <workbookView xWindow="30870" yWindow="1500" windowWidth="20840" windowHeight="13160" xr2:uid="{7FB893FB-0A35-7B43-A2AE-2994BFE54B15}"/>
+    <workbookView xWindow="8950" yWindow="0" windowWidth="16760" windowHeight="13770" xr2:uid="{7FB893FB-0A35-7B43-A2AE-2994BFE54B15}"/>
   </bookViews>
   <sheets>
     <sheet name="Working Tab" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Working Tab'!$A$1:$O$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -171,10 +170,6 @@
   <si>
     <t>CO</t>
     <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physician Administered Drug Fee Schedule
-Immunization Rate Schedule</t>
   </si>
   <si>
     <t>CO Fee Schedules</t>
@@ -1036,12 +1031,16 @@
   <si>
     <t>Downloaded but only PDF</t>
   </si>
+  <si>
+    <t>Physician-Administered Drug Fee Schedule
+Immunization Rate Schedule</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1112,6 +1111,13 @@
       <color theme="7" tint="-0.249977111117893"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1188,11 +1194,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1307,10 +1314,14 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -1768,13 +1779,13 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -1789,7 +1800,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>5</v>
@@ -1814,7 +1825,7 @@
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>11</v>
@@ -1926,7 +1937,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:16380" ht="21" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16380" x14ac:dyDescent="0.4">
       <c r="A5" s="29" t="s">
         <v>27</v>
       </c>
@@ -1935,7 +1946,7 @@
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E5" s="23" t="s">
         <v>11</v>
@@ -18401,10 +18412,10 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>26</v>
@@ -18412,12 +18423,12 @@
     </row>
     <row r="8" spans="1:16380" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="20"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="20"/>
       <c r="E8" s="6" t="s">
         <v>11</v>
@@ -18440,21 +18451,21 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="10" t="s">
         <v>45</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:16380" ht="21" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -18477,25 +18488,25 @@
         <v>0</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:16380" ht="24" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -18520,21 +18531,21 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:16380" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -18557,25 +18568,25 @@
         <v>0</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:16380" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -18600,21 +18611,21 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:16380" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -18639,21 +18650,21 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="O13" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:16380" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -18678,21 +18689,21 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N14" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:16380" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -18717,21 +18728,21 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:16380" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -18756,26 +18767,26 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="N16" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="O16" s="10" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
       <c r="E17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>12</v>
@@ -18784,7 +18795,7 @@
         <v>12</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>12</v>
@@ -18793,25 +18804,25 @@
         <v>0</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -18836,21 +18847,21 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="O18" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
@@ -18858,10 +18869,10 @@
         <v>11</v>
       </c>
       <c r="F19" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>12</v>
@@ -18875,10 +18886,10 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>31</v>
@@ -18886,10 +18897,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20"/>
@@ -18914,21 +18925,21 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="N20" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
@@ -18953,21 +18964,21 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -18992,21 +19003,21 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N22" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="N22" s="9" t="s">
+      <c r="O22" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="O22" s="10" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
@@ -19032,18 +19043,18 @@
       <c r="L23" s="11"/>
       <c r="M23" s="8"/>
       <c r="N23" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="O23" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -19068,21 +19079,21 @@
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
       <c r="M24" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N24" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="O24" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="O24" s="10" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
@@ -19107,21 +19118,21 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="O25" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
@@ -19146,21 +19157,21 @@
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
       <c r="M26" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="O26" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="O26" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -19185,21 +19196,21 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="N27" s="9" t="s">
+      <c r="O27" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -19227,18 +19238,18 @@
         <v>14</v>
       </c>
       <c r="N28" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O28" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
@@ -19263,21 +19274,21 @@
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
       <c r="M29" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N29" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="N29" s="14" t="s">
+      <c r="O29" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -19300,25 +19311,25 @@
         <v>0</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L30" s="11"/>
       <c r="M30" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="N30" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="N30" s="14" t="s">
+      <c r="O30" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="O30" s="10" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="24" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
@@ -19343,21 +19354,21 @@
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
       <c r="M31" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="N31" s="9" t="s">
+      <c r="O31" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
@@ -19382,21 +19393,21 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
       <c r="M32" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="N32" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="O32" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="O32" s="10" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="20"/>
@@ -19421,21 +19432,21 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
       <c r="M33" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N33" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="O33" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
@@ -19460,21 +19471,21 @@
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
       <c r="M34" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N34" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="O34" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
@@ -19499,21 +19510,21 @@
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
       <c r="M35" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="N35" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="O35" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
@@ -19538,21 +19549,21 @@
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
       <c r="M36" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="N36" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="N36" s="14" t="s">
+      <c r="O36" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="O36" s="10" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="20"/>
@@ -19577,21 +19588,21 @@
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N37" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="N37" s="9" t="s">
+      <c r="O37" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
@@ -19616,21 +19627,21 @@
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
       <c r="M38" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="N38" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="N38" s="9" t="s">
+      <c r="O38" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="O38" s="10" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
@@ -19653,25 +19664,25 @@
         <v>0</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L39" s="11"/>
       <c r="M39" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="N39" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="N39" s="9" t="s">
+      <c r="O39" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="21" hidden="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
@@ -19694,25 +19705,25 @@
         <v>0</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L40" s="11"/>
       <c r="M40" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="N40" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="N40" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="O40" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
@@ -19735,25 +19746,25 @@
         <v>0</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L41" s="11"/>
       <c r="M41" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="N41" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="N41" s="9" t="s">
+      <c r="O41" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
@@ -19781,18 +19792,18 @@
         <v>19</v>
       </c>
       <c r="N42" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="O42" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="O42" s="10" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
@@ -19815,25 +19826,25 @@
         <v>0</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L43" s="11"/>
       <c r="M43" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="N43" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="N43" s="14" t="s">
+      <c r="O43" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
@@ -19856,25 +19867,25 @@
         <v>0</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L44" s="11"/>
       <c r="M44" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O44" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="O44" s="10" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
@@ -19899,21 +19910,21 @@
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
       <c r="M45" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N45" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="N45" s="9" t="s">
+      <c r="O45" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="21" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
@@ -19936,23 +19947,23 @@
         <v>0</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L46" s="11"/>
       <c r="M46" s="15"/>
       <c r="N46" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="O46" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="O46" s="10" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="21" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>239</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
@@ -19975,25 +19986,25 @@
         <v>0</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L47" s="11"/>
       <c r="M47" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N47" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="O47" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="21" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
@@ -20016,25 +20027,25 @@
         <v>0</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L48" s="11"/>
       <c r="M48" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="N48" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="N48" s="9" t="s">
+      <c r="O48" s="10" t="s">
         <v>247</v>
-      </c>
-      <c r="O48" s="10" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
@@ -20059,21 +20070,21 @@
       <c r="K49" s="11"/>
       <c r="L49" s="11"/>
       <c r="M49" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="N49" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="N49" s="9" t="s">
+      <c r="O49" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
@@ -20098,21 +20109,21 @@
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>
       <c r="M50" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="N50" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="O50" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="O50" s="10" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>260</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
@@ -20135,25 +20146,25 @@
         <v>0</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L51" s="11"/>
       <c r="M51" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="N51" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="N51" s="9" t="s">
+      <c r="O51" s="10" t="s">
         <v>262</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="21" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="C52" s="20"/>
       <c r="D52" s="20"/>
@@ -20178,13 +20189,13 @@
       <c r="K52" s="11"/>
       <c r="L52" s="11"/>
       <c r="M52" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="N52" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="N52" s="9" t="s">
+      <c r="O52" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.4">
@@ -20354,15 +20365,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="e3650b4f-99d5-4a38-9207-d1f63367a49d">
@@ -20374,7 +20376,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010026B4232F0BA85A4594E917704A667028" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="05eedb731365ed6b09fdb10905a3534b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e3650b4f-99d5-4a38-9207-d1f63367a49d" xmlns:ns3="a44939b3-08bd-462e-9368-13442e4a2529" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="adabcf408cff07f1571985a76b3d6fb0" ns2:_="" ns3:_="">
     <xsd:import namespace="e3650b4f-99d5-4a38-9207-d1f63367a49d"/>
@@ -20587,15 +20589,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDAA5909-A9EB-412D-8D1A-52DA3BA11B01}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F90BB4E-CB0E-4BCF-991B-A615C188294D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20606,7 +20609,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFE0D087-5ABB-4B69-BE0F-7F502E1B8993}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20623,4 +20626,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDAA5909-A9EB-412D-8D1A-52DA3BA11B01}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Fee Schedule Automation Tracker.xlsx
+++ b/Fee Schedule Automation Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petauri-my.sharepoint.com/personal/wonmin_song_petauri_com/Documents/Desktop/Fee-Schedule-Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{D9BA4A1E-E287-2A46-A929-6B1241EC5EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A55ECFA-8EB2-486A-B411-41DFEB81824F}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{D9BA4A1E-E287-2A46-A929-6B1241EC5EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36539664-FE04-43C9-B0D3-C504589B307F}"/>
   <bookViews>
-    <workbookView xWindow="8950" yWindow="0" windowWidth="16760" windowHeight="13770" xr2:uid="{7FB893FB-0A35-7B43-A2AE-2994BFE54B15}"/>
+    <workbookView xWindow="4040" yWindow="0" windowWidth="15150" windowHeight="11370" xr2:uid="{7FB893FB-0A35-7B43-A2AE-2994BFE54B15}"/>
   </bookViews>
   <sheets>
     <sheet name="Working Tab" sheetId="1" r:id="rId1"/>
@@ -1199,7 +1199,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1306,9 +1306,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1316,6 +1313,15 @@
     </xf>
     <xf numFmtId="9" fontId="9" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1852,7 +1858,7 @@
       <c r="M2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="32" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="24" t="s">
@@ -1891,7 +1897,7 @@
       <c r="M3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="32" t="s">
         <v>20</v>
       </c>
       <c r="O3" s="24" t="s">
@@ -1930,7 +1936,7 @@
       <c r="M4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="32" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="24" t="s">
@@ -1971,7 +1977,7 @@
       <c r="M5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="32" t="s">
         <v>30</v>
       </c>
       <c r="O5" s="24" t="s">
@@ -18375,22 +18381,22 @@
       <c r="M6" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="33" t="s">
+      <c r="N6" s="32" t="s">
         <v>36</v>
       </c>
       <c r="O6" s="24" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:16380" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:16380" s="30" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="23" t="s">
         <v>11</v>
       </c>
@@ -18406,18 +18412,18 @@
       <c r="I7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="31" t="s">
+      <c r="J7" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="24" t="s">
         <v>26</v>
       </c>
     </row>
@@ -18428,7 +18434,7 @@
       <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="34"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="20"/>
       <c r="E8" s="6" t="s">
         <v>11</v>
@@ -18450,7 +18456,7 @@
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
-      <c r="M8" s="32" t="s">
+      <c r="M8" s="31" t="s">
         <v>43</v>
       </c>
       <c r="N8" s="9" t="s">
@@ -20365,15 +20371,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e3650b4f-99d5-4a38-9207-d1f63367a49d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a44939b3-08bd-462e-9368-13442e4a2529" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="e3650b4f-99d5-4a38-9207-d1f63367a49d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20590,21 +20593,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e3650b4f-99d5-4a38-9207-d1f63367a49d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a44939b3-08bd-462e-9368-13442e4a2529" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="e3650b4f-99d5-4a38-9207-d1f63367a49d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F90BB4E-CB0E-4BCF-991B-A615C188294D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDAA5909-A9EB-412D-8D1A-52DA3BA11B01}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e3650b4f-99d5-4a38-9207-d1f63367a49d"/>
-    <ds:schemaRef ds:uri="a44939b3-08bd-462e-9368-13442e4a2529"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20629,9 +20632,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDAA5909-A9EB-412D-8D1A-52DA3BA11B01}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F90BB4E-CB0E-4BCF-991B-A615C188294D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e3650b4f-99d5-4a38-9207-d1f63367a49d"/>
+    <ds:schemaRef ds:uri="a44939b3-08bd-462e-9368-13442e4a2529"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>